--- a/demo-data/call-center-demo.xlsx
+++ b/demo-data/call-center-demo.xlsx
@@ -11,30 +11,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="85">
-  <si>
-    <t>Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="83">
+  <si>
+    <t>Customer Name</t>
   </si>
   <si>
     <t>Mobile</t>
   </si>
   <si>
+    <t>Branch</t>
+  </si>
+  <si>
     <t>Source</t>
   </si>
   <si>
-    <t>Branch</t>
+    <t>Model</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Model</t>
+    <t>Remarks</t>
   </si>
   <si>
     <t>SO Name</t>
   </si>
   <si>
-    <t>SO Mobile</t>
+    <t>SO Phone No</t>
   </si>
   <si>
     <t>Status</t>
@@ -46,22 +49,25 @@
     <t>8530001000</t>
   </si>
   <si>
+    <t>C001B</t>
+  </si>
+  <si>
     <t>Meta</t>
   </si>
   <si>
-    <t>Nippon Toyota - Kochi</t>
+    <t>Hyryder</t>
   </si>
   <si>
     <t>Kochi</t>
   </si>
   <si>
-    <t>Hyryder</t>
-  </si>
-  <si>
-    <t>Anil Menon</t>
-  </si>
-  <si>
-    <t>9000001001</t>
+    <t>Need more details</t>
+  </si>
+  <si>
+    <t>Abhijith V M</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Called</t>
@@ -73,22 +79,22 @@
     <t>8530001001</t>
   </si>
   <si>
+    <t>Nippon Toyota - Muvattupuzha</t>
+  </si>
+  <si>
     <t>Referral</t>
   </si>
   <si>
-    <t>Nippon Toyota - Muvattupuzha</t>
+    <t>Glanza</t>
   </si>
   <si>
     <t>Aluva</t>
   </si>
   <si>
-    <t>Glanza</t>
-  </si>
-  <si>
-    <t>Binu Thomas</t>
-  </si>
-  <si>
-    <t>9000001002</t>
+    <t>Planning for later</t>
+  </si>
+  <si>
+    <t>Abhin P A</t>
   </si>
   <si>
     <t>New</t>
@@ -100,22 +106,19 @@
     <t>8530001002</t>
   </si>
   <si>
+    <t>Nippon Toyota - Thiruvalla</t>
+  </si>
+  <si>
     <t>YouTube</t>
   </si>
   <si>
-    <t>Nippon Toyota - Thiruvalla</t>
+    <t>Innova Hycross</t>
   </si>
   <si>
     <t>Kottayam</t>
   </si>
   <si>
-    <t>Innova Hycross</t>
-  </si>
-  <si>
-    <t>Catherine Paul</t>
-  </si>
-  <si>
-    <t>9000001003</t>
+    <t>Adhith Rajesh</t>
   </si>
   <si>
     <t>Arjun Das</t>
@@ -130,10 +133,7 @@
     <t>Thrissur</t>
   </si>
   <si>
-    <t>Dinesh Kumar</t>
-  </si>
-  <si>
-    <t>9000001004</t>
+    <t>Aisil Bose</t>
   </si>
   <si>
     <t>Basil Jose</t>
@@ -142,10 +142,7 @@
     <t>8530001004</t>
   </si>
   <si>
-    <t>Fathima Rahman</t>
-  </si>
-  <si>
-    <t>9000001005</t>
+    <t>Abhilash V Vishnu</t>
   </si>
   <si>
     <t>Devika S</t>
@@ -154,10 +151,7 @@
     <t>8530001005</t>
   </si>
   <si>
-    <t>George Joseph</t>
-  </si>
-  <si>
-    <t>9000001006</t>
+    <t>Abhinav  J</t>
   </si>
   <si>
     <t>Firoz Khan</t>
@@ -652,20 +646,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,124 +689,139 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
       </c>
       <c r="H5" t="s">
         <v>40</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -818,576 +829,636 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
         <v>13</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
         <v>23</v>
       </c>
-      <c r="G6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E11" t="s">
         <v>14</v>
       </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
         <v>16</v>
-      </c>
-      <c r="I8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>39</v>
       </c>
       <c r="H11" t="s">
         <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>57</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>58</v>
       </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C13" t="s">
         <v>31</v>
       </c>
-      <c r="F12" t="s">
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
         <v>23</v>
       </c>
-      <c r="G12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
         <v>38</v>
       </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E17" t="s">
         <v>14</v>
       </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" t="s">
         <v>16</v>
-      </c>
-      <c r="I14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
-        <v>39</v>
       </c>
       <c r="H17" t="s">
         <v>40</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>69</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>70</v>
       </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>13</v>
       </c>
-      <c r="F18" t="s">
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
         <v>23</v>
       </c>
-      <c r="G18" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E23" t="s">
         <v>14</v>
       </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
         <v>16</v>
-      </c>
-      <c r="I20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>39</v>
       </c>
       <c r="H23" t="s">
         <v>40</v>
       </c>
       <c r="I23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>81</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>82</v>
       </c>
-      <c r="C24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="C25" t="s">
         <v>31</v>
       </c>
-      <c r="F24" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" t="s">
-        <v>37</v>
-      </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I25" t="s">
-        <v>26</v>
+        <v>18</v>
+      </c>
+      <c r="J25" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
